--- a/public/documents/k-home-midtown-80-bai-seo.xlsx
+++ b/public/documents/k-home-midtown-80-bai-seo.xlsx
@@ -556,6 +556,9 @@
       <c r="F7" t="str">
         <v>Hỏi đáp / FAQ</v>
       </c>
+      <c r="G7" t="str">
+        <v>Done</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -576,6 +579,9 @@
       <c r="F8" t="str">
         <v>Hỏi đáp / FAQ</v>
       </c>
+      <c r="G8" t="str">
+        <v>Done</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -596,6 +602,9 @@
       <c r="F9" t="str">
         <v>Hỏi đáp / FAQ</v>
       </c>
+      <c r="G9" t="str">
+        <v>Done</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -616,6 +625,9 @@
       <c r="F10" t="str">
         <v>Hỏi đáp / FAQ</v>
       </c>
+      <c r="G10" t="str">
+        <v>Done</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -635,6 +647,9 @@
       </c>
       <c r="F11" t="str">
         <v>Hỏi đáp / FAQ</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Done</v>
       </c>
     </row>
     <row r="12">
